--- a/nma/demo/nma_report.xlsx
+++ b/nma/demo/nma_report.xlsx
@@ -321,10 +321,1419 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="337">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -335,7 +1744,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="204">
     <border>
       <left/>
       <right/>
@@ -343,12 +1752,2164 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0"/>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="155" xfId="0"/>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,264 +3921,271 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="2" customWidth="true"/>
+    <col min="3" max="6" width="14.7109375" style="3" customWidth="true"/>
+    <col min="7" max="7" width="12.7109375" style="4" customWidth="true"/>
+    <col min="8" max="8" width="12.7109375" style="5" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="53" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="61" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="69" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="77" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="85" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="93" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="101" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="109" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="117" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="125" t="s">
         <v>61</v>
       </c>
     </row>
@@ -629,68 +4197,72 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" style="126" customWidth="true"/>
+    <col min="2" max="2" width="25.7109375" style="127" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="139" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="141" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="142" t="s">
         <v>65</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="143" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="144" t="s">
         <v>66</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="145" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="147" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="148" t="s">
         <v>68</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="149" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="151" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="153" t="s">
         <v>77</v>
       </c>
     </row>
@@ -702,125 +4274,129 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="154" customWidth="true"/>
+    <col min="2" max="3" width="14.7109375" style="155" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="173" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="175" t="s">
         <v>79</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="176" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="178" t="s">
         <v>80</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="179" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="181" t="s">
         <v>81</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="182" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="184" t="s">
         <v>82</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="185" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="186" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="187" t="s">
         <v>83</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="188" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="189" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="190" t="s">
         <v>84</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="191" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="192" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="193" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="194" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="196" t="s">
         <v>86</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="197" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="199" t="s">
         <v>87</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="200" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="203" t="s">
         <v>99</v>
       </c>
     </row>
